--- a/Scdat_Project_2026_Architechture.xlsx
+++ b/Scdat_Project_2026_Architechture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JAFAR\STREAMLIT\Scdat_Project_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73563A60-D875-4840-949B-D64668428F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704D5EBA-67F7-49DF-9C64-A396E410DC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{674A2B4B-77A8-4448-93CC-6DB6767CCAC3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>data.sales_trend_df(datafile_location, supplier, model, month_list)</t>
   </si>
@@ -124,13 +124,16 @@
   </si>
   <si>
     <t>data.wh_wise_inventory_df(datafile_location) - return df_wh, df_wh1, df_wh2, df_wh3, df_wh4, df_parts, df_box, df_refurb, df_container, df_retail, retail_models, df_faucet, df_bathtub</t>
+  </si>
+  <si>
+    <t>weekly_container_arrival_chart(datafile_location, supplier, model)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -139,59 +142,65 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FFC00000"/>
-      <name val="Calibri"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="5" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <color rgb="FF0070C0"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF7030A0"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -254,105 +263,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -672,22 +660,22 @@
   <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="7" customWidth="1"/>
-    <col min="3" max="3" width="61.140625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="64.85546875" style="28" customWidth="1"/>
-    <col min="5" max="5" width="63.5703125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="23.28515625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="20" style="10" customWidth="1"/>
+    <col min="3" max="3" width="61.140625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="64.85546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="79.7109375" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -695,345 +683,354 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="23"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="31" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="4" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="31" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="4" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="8" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="10"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="8"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="31" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="31" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="15"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="10"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="19" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="8"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="15"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="31" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="15"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="31" t="s">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="15"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="31" t="s">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="15"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="8" t="s">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="19" t="s">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="15"/>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="15"/>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="15"/>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="8"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="8"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="15"/>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="10"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="33"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="14"/>
       <c r="E26" s="15"/>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="33"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="14"/>
       <c r="E27" s="15"/>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="10"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
-      <c r="B29" s="16" t="s">
+      <c r="A29" s="11"/>
+      <c r="B29" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="33"/>
+      <c r="D29" s="14"/>
       <c r="E29" s="15"/>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="33" t="s">
+      <c r="A30" s="11"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="14" t="s">
         <v>30</v>
       </c>
       <c r="E30" s="15"/>
     </row>
     <row r="31" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="14"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="33" t="s">
+      <c r="A31" s="11"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E31" s="15"/>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="10"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="19"/>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="14"/>
-      <c r="B33" s="16" t="s">
+      <c r="A33" s="11"/>
+      <c r="B33" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="33"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="14"/>
       <c r="E33" s="15"/>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="33"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="14"/>
       <c r="E34" s="15"/>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="33"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="14"/>
       <c r="E35" s="15"/>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="14"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="10"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="19"/>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D38" s="31" t="s">
+    <row r="38" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="23"/>
+      <c r="D38" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E39" s="4" t="s">
+      <c r="B39" s="23"/>
+      <c r="E39" s="15" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E40" s="4"/>
+      <c r="B40" s="23"/>
+      <c r="E40" s="15"/>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E41" s="4" t="s">
+      <c r="B41" s="23"/>
+      <c r="E41" s="15" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E42" s="4" t="s">
+      <c r="B42" s="23"/>
+      <c r="E42" s="15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E43" s="4" t="s">
+      <c r="B43" s="23"/>
+      <c r="E43" s="15" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E44" s="4" t="s">
+      <c r="B44" s="23"/>
+      <c r="E44" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="11"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="19" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
